--- a/pages/WR_progressions/Men_IP.xlsx
+++ b/pages/WR_progressions/Men_IP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\WR_progressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF231D7C-8527-4F88-B9A6-E1AF53BBCA19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA5EDFA-6C4A-44EF-A223-62C23B1763D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{85857209-E43F-45C1-9B39-A662482E439E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{85857209-E43F-45C1-9B39-A662482E439E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="mm:ss.000"/>
+    <numFmt numFmtId="164" formatCode="mm:ss.000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -89,7 +89,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -424,7 +424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8047C023-39BC-4DC0-983B-FBBE8975FD0C}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="9.9296875" bestFit="1" customWidth="1"/>
@@ -465,14 +465,14 @@
         <v>3.0472569444444444E-3</v>
       </c>
       <c r="B3">
-        <f t="shared" ref="B3:B17" si="0">A3*86400</f>
+        <f t="shared" ref="B3:B18" si="0">A3*86400</f>
         <v>263.28300000000002</v>
       </c>
       <c r="C3" s="1">
         <v>34199</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D17" si="1">C3</f>
+        <f t="shared" ref="D3:D18" si="1">C3</f>
         <v>34199</v>
       </c>
     </row>
@@ -698,6 +698,22 @@
       <c r="D17">
         <f t="shared" si="1"/>
         <v>44848</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A18" s="2">
+        <v>2.7679745370370371E-3</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="0"/>
+        <v>239.15300000000002</v>
+      </c>
+      <c r="C18" s="1">
+        <v>45583</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="1"/>
+        <v>45583</v>
       </c>
     </row>
   </sheetData>
